--- a/data/output/swing_agent.xlsx
+++ b/data/output/swing_agent.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Setups for the session after 2026-09-25 · generated 2026-09-27 18:40 IST</t>
+          <t>Setups for the session after 2026-09-25 · generated 2026-09-27 18:44 IST</t>
         </is>
       </c>
     </row>

--- a/data/output/swing_agent.xlsx
+++ b/data/output/swing_agent.xlsx
@@ -547,7 +547,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Setups for the session after 2026-09-25 · generated 2026-09-27 18:44 IST</t>
+          <t>Setups for the session after 2026-09-25 · generated 2026-09-27 18:52 IST</t>
         </is>
       </c>
     </row>
